--- a/RackWorks/rack_layout_top_down.xlsx
+++ b/RackWorks/rack_layout_top_down.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -496,17 +496,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Device Name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Height</t>
+          <t>Device</t>
         </is>
       </c>
     </row>
@@ -517,8 +507,6 @@
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr"/>
-      <c r="C2" s="3" t="inlineStr"/>
-      <c r="D2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -527,8 +515,6 @@
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -537,8 +523,6 @@
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr"/>
-      <c r="C4" s="3" t="inlineStr"/>
-      <c r="D4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -547,8 +531,6 @@
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr"/>
-      <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -557,8 +539,6 @@
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr"/>
-      <c r="C6" s="3" t="inlineStr"/>
-      <c r="D6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -567,8 +547,6 @@
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -577,8 +555,6 @@
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr"/>
-      <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -587,8 +563,6 @@
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr"/>
-      <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -600,21 +574,11 @@
         <is>
           <t>compute_nodes_1</t>
         </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Compute Nodes</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
       <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -623,8 +587,6 @@
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr"/>
-      <c r="C12" s="3" t="inlineStr"/>
-      <c r="D12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -633,8 +595,6 @@
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr"/>
-      <c r="C13" s="3" t="inlineStr"/>
-      <c r="D13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -643,8 +603,6 @@
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr"/>
-      <c r="C14" s="3" t="inlineStr"/>
-      <c r="D14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -653,8 +611,6 @@
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr"/>
-      <c r="C15" s="3" t="inlineStr"/>
-      <c r="D15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -663,8 +619,6 @@
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr"/>
-      <c r="C16" s="3" t="inlineStr"/>
-      <c r="D16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -673,8 +627,6 @@
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr"/>
-      <c r="C17" s="3" t="inlineStr"/>
-      <c r="D17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -683,8 +635,6 @@
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr"/>
-      <c r="C18" s="3" t="inlineStr"/>
-      <c r="D18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -693,8 +643,6 @@
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr"/>
-      <c r="C19" s="3" t="inlineStr"/>
-      <c r="D19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -703,8 +651,6 @@
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr"/>
-      <c r="C20" s="3" t="inlineStr"/>
-      <c r="D20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -713,8 +659,6 @@
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr"/>
-      <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -723,8 +667,6 @@
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr"/>
-      <c r="C22" s="3" t="inlineStr"/>
-      <c r="D22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -736,21 +678,11 @@
         <is>
           <t>LAN_3__S_xx64_2</t>
         </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>LAN Switch</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
       <c r="B24" s="5" t="n"/>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="5" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -759,8 +691,6 @@
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr"/>
-      <c r="C25" s="3" t="inlineStr"/>
-      <c r="D25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -772,21 +702,11 @@
         <is>
           <t>LAN_2__Z_9xxx_3</t>
         </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>LAN Switch</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n"/>
       <c r="B27" s="5" t="n"/>
-      <c r="C27" s="5" t="n"/>
-      <c r="D27" s="5" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -795,8 +715,6 @@
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr"/>
-      <c r="C28" s="3" t="inlineStr"/>
-      <c r="D28" s="3" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
@@ -808,33 +726,19 @@
         <is>
           <t>GPU_nodes_4</t>
         </is>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>Gpu Nodes</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="n"/>
       <c r="B30" s="8" t="n"/>
-      <c r="C30" s="8" t="n"/>
-      <c r="D30" s="8" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="8" t="n"/>
       <c r="B31" s="8" t="n"/>
-      <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n"/>
       <c r="B32" s="5" t="n"/>
-      <c r="C32" s="5" t="n"/>
-      <c r="D32" s="5" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -843,8 +747,6 @@
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr"/>
-      <c r="C33" s="3" t="inlineStr"/>
-      <c r="D33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -853,8 +755,6 @@
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr"/>
-      <c r="C34" s="3" t="inlineStr"/>
-      <c r="D34" s="3" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -863,8 +763,6 @@
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr"/>
-      <c r="C35" s="3" t="inlineStr"/>
-      <c r="D35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -876,21 +774,11 @@
         <is>
           <t>compute_nodes_5</t>
         </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>Compute Nodes</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n"/>
       <c r="B37" s="5" t="n"/>
-      <c r="C37" s="5" t="n"/>
-      <c r="D37" s="5" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -899,8 +787,6 @@
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr"/>
-      <c r="C38" s="3" t="inlineStr"/>
-      <c r="D38" s="3" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -909,8 +795,6 @@
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr"/>
-      <c r="C39" s="3" t="inlineStr"/>
-      <c r="D39" s="3" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -919,8 +803,6 @@
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr"/>
-      <c r="C40" s="3" t="inlineStr"/>
-      <c r="D40" s="3" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -929,8 +811,6 @@
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr"/>
-      <c r="C41" s="3" t="inlineStr"/>
-      <c r="D41" s="3" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -939,8 +819,6 @@
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr"/>
-      <c r="C42" s="3" t="inlineStr"/>
-      <c r="D42" s="3" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -949,30 +827,18 @@
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr"/>
-      <c r="C43" s="3" t="inlineStr"/>
-      <c r="D43" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
-    <mergeCell ref="C29:C32"/>
+  <mergeCells count="10">
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A23:A24"/>
     <mergeCell ref="A36:A37"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A29:A32"/>
+    <mergeCell ref="B10:B11"/>
     <mergeCell ref="B29:B32"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="A29:A32"/>
     <mergeCell ref="A10:A11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="D29:D32"/>
     <mergeCell ref="B26:B27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/RackWorks/rack_layout_top_down.xlsx
+++ b/RackWorks/rack_layout_top_down.xlsx
@@ -97,23 +97,27 @@
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>

--- a/RackWorks/rack_layout_top_down.xlsx
+++ b/RackWorks/rack_layout_top_down.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Rack Layout" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rack_0" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rack_1" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -29,7 +30,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -52,6 +53,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="0099CCFF"/>
         <bgColor rgb="0099CCFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
+        <bgColor rgb="00FFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -94,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -102,20 +115,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -483,11 +498,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
   </cols>
@@ -503,6 +518,16 @@
           <t>Device</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Wattage (W)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Weight (kg)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -510,7 +535,9 @@
           <t>42</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr"/>
+      <c r="B2" s="2" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -518,7 +545,9 @@
           <t>41</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr"/>
+      <c r="B3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -526,7 +555,9 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr"/>
+      <c r="B4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -534,7 +565,9 @@
           <t>39</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr"/>
+      <c r="B5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -542,7 +575,9 @@
           <t>38</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -550,7 +585,9 @@
           <t>37</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr"/>
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -558,7 +595,9 @@
           <t>36</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr"/>
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -566,23 +605,33 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr"/>
+      <c r="D9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>33-34</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>compute_nodes_1</t>
         </is>
       </c>
+      <c r="C10" s="3" t="n">
+        <v>1350</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>28.7</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="n"/>
+      <c r="A11" s="8" t="n"/>
+      <c r="B11" s="8" t="n"/>
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -590,7 +639,9 @@
           <t>32</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr"/>
+      <c r="C12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -598,7 +649,9 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr"/>
+      <c r="C13" s="2" t="inlineStr"/>
+      <c r="D13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -606,7 +659,9 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr"/>
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -614,7 +669,9 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr"/>
+      <c r="C15" s="2" t="inlineStr"/>
+      <c r="D15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -622,7 +679,9 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr"/>
+      <c r="C16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -630,7 +689,9 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr"/>
+      <c r="C17" s="2" t="inlineStr"/>
+      <c r="D17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -638,7 +699,9 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr"/>
+      <c r="C18" s="2" t="inlineStr"/>
+      <c r="D18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -646,7 +709,9 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr"/>
+      <c r="C19" s="2" t="inlineStr"/>
+      <c r="D19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -654,7 +719,9 @@
           <t>24</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr"/>
+      <c r="C20" s="2" t="inlineStr"/>
+      <c r="D20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -662,87 +729,127 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr"/>
+      <c r="C21" s="2" t="inlineStr"/>
+      <c r="D21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr"/>
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>21-22</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>LAN_3__S_xx64_2</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>300</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>20-21</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>LAN_3__S_xx64_2</t>
-        </is>
-      </c>
+      <c r="A23" s="8" t="n"/>
+      <c r="B23" s="8" t="n"/>
+      <c r="C23" s="8" t="n"/>
+      <c r="D23" s="8" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n"/>
-      <c r="B24" s="5" t="n"/>
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>19-20</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>LAN_2__Z_9xxx_3</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>1304</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr"/>
+      <c r="A25" s="8" t="n"/>
+      <c r="B25" s="8" t="n"/>
+      <c r="C25" s="8" t="n"/>
+      <c r="D25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>17-18</t>
+          <t>15-18</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>LAN_2__Z_9xxx_3</t>
-        </is>
+          <t>GPU_nodes_4</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>11660</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>61.4</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n"/>
-      <c r="B27" s="5" t="n"/>
+      <c r="A27" s="9" t="n"/>
+      <c r="B27" s="9" t="n"/>
+      <c r="C27" s="9" t="n"/>
+      <c r="D27" s="9" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr"/>
+      <c r="A28" s="9" t="n"/>
+      <c r="B28" s="9" t="n"/>
+      <c r="C28" s="9" t="n"/>
+      <c r="D28" s="9" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>GPU_nodes_4</t>
-        </is>
-      </c>
+      <c r="A29" s="8" t="n"/>
+      <c r="B29" s="8" t="n"/>
+      <c r="C29" s="8" t="n"/>
+      <c r="D29" s="8" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="n"/>
-      <c r="B30" s="8" t="n"/>
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>13-14</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>compute_nodes_5</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>1350</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>28.7</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="n"/>
       <c r="B31" s="8" t="n"/>
+      <c r="C31" s="8" t="n"/>
+      <c r="D31" s="8" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n"/>
-      <c r="B32" s="5" t="n"/>
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr"/>
+      <c r="D32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -750,7 +857,9 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr"/>
+      <c r="D33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -758,7 +867,9 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr"/>
+      <c r="D34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -766,23 +877,29 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr"/>
+      <c r="D35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>7-8</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>compute_nodes_5</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr"/>
+      <c r="D36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n"/>
-      <c r="B37" s="5" t="n"/>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr"/>
+      <c r="D37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -790,7 +907,9 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr"/>
+      <c r="D38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -798,7 +917,9 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr"/>
+      <c r="D39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -806,7 +927,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr"/>
+      <c r="D40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -814,7 +937,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr"/>
+      <c r="D41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -822,7 +947,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr"/>
+      <c r="D42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -830,20 +957,540 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr"/>
+      <c r="D43" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr"/>
+      <c r="C45" s="7" t="n">
+        <v>15964</v>
+      </c>
+      <c r="D45" s="7" t="n">
+        <v>150.8</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A29:A32"/>
+  <mergeCells count="20">
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="C26:C29"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="C22:C23"/>
     <mergeCell ref="B10:B11"/>
-    <mergeCell ref="B29:B32"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A26:A29"/>
     <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="D26:D29"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="D22:D23"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Rack Position</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Device</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Wattage (W)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Weight (kg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr"/>
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr"/>
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr"/>
+      <c r="D9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr"/>
+      <c r="C10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr"/>
+      <c r="C11" s="2" t="inlineStr"/>
+      <c r="D11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr"/>
+      <c r="C12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr"/>
+      <c r="C13" s="2" t="inlineStr"/>
+      <c r="D13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr"/>
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr"/>
+      <c r="C15" s="2" t="inlineStr"/>
+      <c r="D15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr"/>
+      <c r="C16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr"/>
+      <c r="C17" s="2" t="inlineStr"/>
+      <c r="D17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr"/>
+      <c r="C18" s="2" t="inlineStr"/>
+      <c r="D18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr"/>
+      <c r="C19" s="2" t="inlineStr"/>
+      <c r="D19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr"/>
+      <c r="C20" s="2" t="inlineStr"/>
+      <c r="D20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>22-23</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>LAN_1__IB+400_1</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>21-21</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>NVMenodes_1</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="n">
+        <v>1128</v>
+      </c>
+      <c r="D23" s="10" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr"/>
+      <c r="D24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr"/>
+      <c r="D25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr"/>
+      <c r="D26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr"/>
+      <c r="D27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr"/>
+      <c r="D28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr"/>
+      <c r="D29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr"/>
+      <c r="D31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr"/>
+      <c r="D32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr"/>
+      <c r="D33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr"/>
+      <c r="D34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr"/>
+      <c r="D35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr"/>
+      <c r="D36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr"/>
+      <c r="D37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr"/>
+      <c r="D38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr"/>
+      <c r="D39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr"/>
+      <c r="D40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr"/>
+      <c r="D41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr"/>
+      <c r="D42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr"/>
+      <c r="D43" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr"/>
+      <c r="C45" s="7" t="n">
+        <v>3128</v>
+      </c>
+      <c r="D45" s="7" t="n">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="A21:A22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/RackWorks/rack_layout_top_down.xlsx
+++ b/RackWorks/rack_layout_top_down.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Rack_0" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Rack_1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Rack_1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rack_2" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -39,14 +39,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FF9999"/>
-        <bgColor rgb="00FF9999"/>
+        <fgColor rgb="0099FF99"/>
+        <bgColor rgb="0099FF99"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0099FF99"/>
-        <bgColor rgb="0099FF99"/>
+        <fgColor rgb="00FF9999"/>
+        <bgColor rgb="00FF9999"/>
       </patternFill>
     </fill>
     <fill>
@@ -63,8 +63,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="001C81CE"/>
+        <bgColor rgb="001C81CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -112,13 +112,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -532,248 +532,248 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr"/>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr"/>
+          <t>41-42</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>LAN_2__Z_9xxx_41</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>1304</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr"/>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr"/>
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr"/>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr"/>
+          <t>39-40</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>LAN_3__S_xx64_39</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr"/>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr"/>
+      <c r="A5" s="8" t="n"/>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr"/>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr"/>
+      <c r="B6" s="4" t="inlineStr"/>
+      <c r="C6" s="4" t="inlineStr"/>
+      <c r="D6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr"/>
-      <c r="C7" s="2" t="inlineStr"/>
-      <c r="D7" s="2" t="inlineStr"/>
+      <c r="B7" s="4" t="inlineStr"/>
+      <c r="C7" s="4" t="inlineStr"/>
+      <c r="D7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr"/>
-      <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr"/>
+      <c r="B8" s="4" t="inlineStr"/>
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr"/>
-      <c r="C9" s="2" t="inlineStr"/>
-      <c r="D9" s="2" t="inlineStr"/>
+      <c r="B9" s="4" t="inlineStr"/>
+      <c r="C9" s="4" t="inlineStr"/>
+      <c r="D9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>33-34</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>compute_nodes_1</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="n">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr"/>
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr"/>
+      <c r="C11" s="4" t="inlineStr"/>
+      <c r="D11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr"/>
+      <c r="C12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr"/>
+      <c r="C13" s="4" t="inlineStr"/>
+      <c r="D13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr"/>
+      <c r="C14" s="4" t="inlineStr"/>
+      <c r="D14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr"/>
+      <c r="C15" s="4" t="inlineStr"/>
+      <c r="D15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4" t="inlineStr"/>
+      <c r="D16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr"/>
+      <c r="C17" s="4" t="inlineStr"/>
+      <c r="D17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>compute_nodes_25</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
         <v>1350</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D18" s="5" t="n">
         <v>28.7</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="8" t="n"/>
-      <c r="B11" s="8" t="n"/>
-      <c r="C11" s="8" t="n"/>
-      <c r="D11" s="8" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr"/>
-      <c r="C12" s="2" t="inlineStr"/>
-      <c r="D12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr"/>
-      <c r="C13" s="2" t="inlineStr"/>
-      <c r="D13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr"/>
-      <c r="C14" s="2" t="inlineStr"/>
-      <c r="D14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr"/>
-      <c r="C15" s="2" t="inlineStr"/>
-      <c r="D15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr"/>
-      <c r="C16" s="2" t="inlineStr"/>
-      <c r="D16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr"/>
-      <c r="C17" s="2" t="inlineStr"/>
-      <c r="D17" s="2" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr"/>
-      <c r="C18" s="2" t="inlineStr"/>
-      <c r="D18" s="2" t="inlineStr"/>
-    </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr"/>
-      <c r="C19" s="2" t="inlineStr"/>
-      <c r="D19" s="2" t="inlineStr"/>
+      <c r="A19" s="8" t="n"/>
+      <c r="B19" s="8" t="n"/>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="8" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr"/>
-      <c r="C20" s="2" t="inlineStr"/>
-      <c r="D20" s="2" t="inlineStr"/>
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>23-24</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>compute_nodes_23</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>1350</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>28.7</v>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr"/>
-      <c r="C21" s="2" t="inlineStr"/>
-      <c r="D21" s="2" t="inlineStr"/>
+      <c r="A21" s="8" t="n"/>
+      <c r="B21" s="8" t="n"/>
+      <c r="C21" s="8" t="n"/>
+      <c r="D21" s="8" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>21-22</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>LAN_3__S_xx64_2</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="n">
-        <v>300</v>
-      </c>
-      <c r="D22" s="5" t="n">
-        <v>12</v>
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>19-22</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>GPU_nodes_19</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>11660</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>61.4</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="n"/>
-      <c r="B23" s="8" t="n"/>
-      <c r="C23" s="8" t="n"/>
-      <c r="D23" s="8" t="n"/>
+      <c r="A23" s="9" t="n"/>
+      <c r="B23" s="9" t="n"/>
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="9" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>19-20</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>LAN_2__Z_9xxx_3</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="n">
-        <v>1304</v>
-      </c>
-      <c r="D24" s="5" t="n">
-        <v>20</v>
-      </c>
+      <c r="A24" s="9" t="n"/>
+      <c r="B24" s="9" t="n"/>
+      <c r="C24" s="9" t="n"/>
+      <c r="D24" s="9" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="8" t="n"/>
@@ -782,184 +782,184 @@
       <c r="D25" s="8" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>15-18</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>GPU_nodes_4</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="n">
-        <v>11660</v>
-      </c>
-      <c r="D26" s="6" t="n">
-        <v>61.4</v>
-      </c>
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr"/>
+      <c r="C26" s="4" t="inlineStr"/>
+      <c r="D26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="n"/>
-      <c r="B27" s="9" t="n"/>
-      <c r="C27" s="9" t="n"/>
-      <c r="D27" s="9" t="n"/>
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr"/>
+      <c r="C27" s="4" t="inlineStr"/>
+      <c r="D27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="n"/>
-      <c r="B28" s="9" t="n"/>
-      <c r="C28" s="9" t="n"/>
-      <c r="D28" s="9" t="n"/>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr"/>
+      <c r="C28" s="4" t="inlineStr"/>
+      <c r="D28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="n"/>
-      <c r="B29" s="8" t="n"/>
-      <c r="C29" s="8" t="n"/>
-      <c r="D29" s="8" t="n"/>
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr"/>
+      <c r="C29" s="4" t="inlineStr"/>
+      <c r="D29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>13-14</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>compute_nodes_5</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="n">
-        <v>1350</v>
-      </c>
-      <c r="D30" s="3" t="n">
-        <v>28.7</v>
-      </c>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr"/>
+      <c r="C30" s="4" t="inlineStr"/>
+      <c r="D30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="n"/>
-      <c r="B31" s="8" t="n"/>
-      <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8" t="n"/>
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr"/>
+      <c r="C31" s="4" t="inlineStr"/>
+      <c r="D31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr"/>
-      <c r="C32" s="2" t="inlineStr"/>
-      <c r="D32" s="2" t="inlineStr"/>
+      <c r="B32" s="4" t="inlineStr"/>
+      <c r="C32" s="4" t="inlineStr"/>
+      <c r="D32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr"/>
-      <c r="C33" s="2" t="inlineStr"/>
-      <c r="D33" s="2" t="inlineStr"/>
+      <c r="B33" s="4" t="inlineStr"/>
+      <c r="C33" s="4" t="inlineStr"/>
+      <c r="D33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr"/>
-      <c r="C34" s="2" t="inlineStr"/>
-      <c r="D34" s="2" t="inlineStr"/>
+      <c r="B34" s="4" t="inlineStr"/>
+      <c r="C34" s="4" t="inlineStr"/>
+      <c r="D34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr"/>
-      <c r="C35" s="2" t="inlineStr"/>
-      <c r="D35" s="2" t="inlineStr"/>
+      <c r="B35" s="4" t="inlineStr"/>
+      <c r="C35" s="4" t="inlineStr"/>
+      <c r="D35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr"/>
-      <c r="C36" s="2" t="inlineStr"/>
-      <c r="D36" s="2" t="inlineStr"/>
+      <c r="B36" s="4" t="inlineStr"/>
+      <c r="C36" s="4" t="inlineStr"/>
+      <c r="D36" s="4" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr"/>
-      <c r="C37" s="2" t="inlineStr"/>
-      <c r="D37" s="2" t="inlineStr"/>
+      <c r="B37" s="4" t="inlineStr"/>
+      <c r="C37" s="4" t="inlineStr"/>
+      <c r="D37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr"/>
-      <c r="C38" s="2" t="inlineStr"/>
-      <c r="D38" s="2" t="inlineStr"/>
+      <c r="B38" s="4" t="inlineStr"/>
+      <c r="C38" s="4" t="inlineStr"/>
+      <c r="D38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr"/>
-      <c r="C39" s="2" t="inlineStr"/>
-      <c r="D39" s="2" t="inlineStr"/>
+      <c r="B39" s="4" t="inlineStr"/>
+      <c r="C39" s="4" t="inlineStr"/>
+      <c r="D39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr"/>
-      <c r="C40" s="2" t="inlineStr"/>
-      <c r="D40" s="2" t="inlineStr"/>
+      <c r="B40" s="4" t="inlineStr"/>
+      <c r="C40" s="4" t="inlineStr"/>
+      <c r="D40" s="4" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr"/>
-      <c r="C41" s="2" t="inlineStr"/>
-      <c r="D41" s="2" t="inlineStr"/>
+      <c r="B41" s="4" t="inlineStr"/>
+      <c r="C41" s="4" t="inlineStr"/>
+      <c r="D41" s="4" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr"/>
-      <c r="C42" s="2" t="inlineStr"/>
-      <c r="D42" s="2" t="inlineStr"/>
+      <c r="B42" s="4" t="inlineStr"/>
+      <c r="C42" s="4" t="inlineStr"/>
+      <c r="D42" s="4" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr"/>
-      <c r="C43" s="2" t="inlineStr"/>
-      <c r="D43" s="2" t="inlineStr"/>
+      <c r="B43" s="4" t="inlineStr"/>
+      <c r="C43" s="4" t="inlineStr"/>
+      <c r="D43" s="4" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
@@ -977,26 +977,26 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="C26:C29"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A26:A29"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="B26:B29"/>
-    <mergeCell ref="D26:D29"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="D22:D25"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="C22:C25"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C18:C19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1042,216 +1042,216 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr"/>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr"/>
+          <t>41-42</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>LAN_1__IB+400_41</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr"/>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr"/>
+      <c r="A3" s="3" t="n"/>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr"/>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr"/>
+      <c r="B4" s="4" t="inlineStr"/>
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr"/>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr"/>
+      <c r="B5" s="4" t="inlineStr"/>
+      <c r="C5" s="4" t="inlineStr"/>
+      <c r="D5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr"/>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr"/>
+      <c r="B6" s="4" t="inlineStr"/>
+      <c r="C6" s="4" t="inlineStr"/>
+      <c r="D6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr"/>
-      <c r="C7" s="2" t="inlineStr"/>
-      <c r="D7" s="2" t="inlineStr"/>
+      <c r="B7" s="4" t="inlineStr"/>
+      <c r="C7" s="4" t="inlineStr"/>
+      <c r="D7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr"/>
-      <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr"/>
+      <c r="B8" s="4" t="inlineStr"/>
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr"/>
-      <c r="C9" s="2" t="inlineStr"/>
-      <c r="D9" s="2" t="inlineStr"/>
+      <c r="B9" s="4" t="inlineStr"/>
+      <c r="C9" s="4" t="inlineStr"/>
+      <c r="D9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr"/>
-      <c r="C10" s="2" t="inlineStr"/>
-      <c r="D10" s="2" t="inlineStr"/>
+      <c r="B10" s="4" t="inlineStr"/>
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr"/>
-      <c r="C11" s="2" t="inlineStr"/>
-      <c r="D11" s="2" t="inlineStr"/>
+      <c r="B11" s="4" t="inlineStr"/>
+      <c r="C11" s="4" t="inlineStr"/>
+      <c r="D11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr"/>
-      <c r="C12" s="2" t="inlineStr"/>
-      <c r="D12" s="2" t="inlineStr"/>
+      <c r="B12" s="4" t="inlineStr"/>
+      <c r="C12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr"/>
-      <c r="C13" s="2" t="inlineStr"/>
-      <c r="D13" s="2" t="inlineStr"/>
+      <c r="B13" s="4" t="inlineStr"/>
+      <c r="C13" s="4" t="inlineStr"/>
+      <c r="D13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr"/>
-      <c r="C14" s="2" t="inlineStr"/>
-      <c r="D14" s="2" t="inlineStr"/>
+      <c r="B14" s="4" t="inlineStr"/>
+      <c r="C14" s="4" t="inlineStr"/>
+      <c r="D14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr"/>
-      <c r="C15" s="2" t="inlineStr"/>
-      <c r="D15" s="2" t="inlineStr"/>
+      <c r="B15" s="4" t="inlineStr"/>
+      <c r="C15" s="4" t="inlineStr"/>
+      <c r="D15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr"/>
-      <c r="C16" s="2" t="inlineStr"/>
-      <c r="D16" s="2" t="inlineStr"/>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4" t="inlineStr"/>
+      <c r="D16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr"/>
-      <c r="C17" s="2" t="inlineStr"/>
-      <c r="D17" s="2" t="inlineStr"/>
+      <c r="B17" s="4" t="inlineStr"/>
+      <c r="C17" s="4" t="inlineStr"/>
+      <c r="D17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr"/>
-      <c r="C18" s="2" t="inlineStr"/>
-      <c r="D18" s="2" t="inlineStr"/>
+      <c r="B18" s="4" t="inlineStr"/>
+      <c r="C18" s="4" t="inlineStr"/>
+      <c r="D18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr"/>
-      <c r="C19" s="2" t="inlineStr"/>
-      <c r="D19" s="2" t="inlineStr"/>
+      <c r="B19" s="4" t="inlineStr"/>
+      <c r="C19" s="4" t="inlineStr"/>
+      <c r="D19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr"/>
-      <c r="C20" s="2" t="inlineStr"/>
-      <c r="D20" s="2" t="inlineStr"/>
+      <c r="B20" s="4" t="inlineStr"/>
+      <c r="C20" s="4" t="inlineStr"/>
+      <c r="D20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>22-23</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>LAN_1__IB+400_1</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="n">
-        <v>2000</v>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>20</v>
-      </c>
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr"/>
+      <c r="C21" s="4" t="inlineStr"/>
+      <c r="D21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="n"/>
-      <c r="B22" s="4" t="n"/>
-      <c r="C22" s="4" t="n"/>
-      <c r="D22" s="4" t="n"/>
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr"/>
+      <c r="C22" s="4" t="inlineStr"/>
+      <c r="D22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>NVMenodes_1</t>
+          <t>NVMenodes_21</t>
         </is>
       </c>
       <c r="C23" s="10" t="n">
@@ -1272,204 +1272,204 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr"/>
-      <c r="C24" s="2" t="inlineStr"/>
-      <c r="D24" s="2" t="inlineStr"/>
+      <c r="B24" s="4" t="inlineStr"/>
+      <c r="C24" s="4" t="inlineStr"/>
+      <c r="D24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr"/>
-      <c r="C25" s="2" t="inlineStr"/>
-      <c r="D25" s="2" t="inlineStr"/>
+      <c r="B25" s="4" t="inlineStr"/>
+      <c r="C25" s="4" t="inlineStr"/>
+      <c r="D25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr"/>
-      <c r="C26" s="2" t="inlineStr"/>
-      <c r="D26" s="2" t="inlineStr"/>
+      <c r="B26" s="4" t="inlineStr"/>
+      <c r="C26" s="4" t="inlineStr"/>
+      <c r="D26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr"/>
-      <c r="C27" s="2" t="inlineStr"/>
-      <c r="D27" s="2" t="inlineStr"/>
+      <c r="B27" s="4" t="inlineStr"/>
+      <c r="C27" s="4" t="inlineStr"/>
+      <c r="D27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr"/>
-      <c r="C28" s="2" t="inlineStr"/>
-      <c r="D28" s="2" t="inlineStr"/>
+      <c r="B28" s="4" t="inlineStr"/>
+      <c r="C28" s="4" t="inlineStr"/>
+      <c r="D28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr"/>
-      <c r="C29" s="2" t="inlineStr"/>
-      <c r="D29" s="2" t="inlineStr"/>
+      <c r="B29" s="4" t="inlineStr"/>
+      <c r="C29" s="4" t="inlineStr"/>
+      <c r="D29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr"/>
-      <c r="C30" s="2" t="inlineStr"/>
-      <c r="D30" s="2" t="inlineStr"/>
+      <c r="B30" s="4" t="inlineStr"/>
+      <c r="C30" s="4" t="inlineStr"/>
+      <c r="D30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr"/>
-      <c r="C31" s="2" t="inlineStr"/>
-      <c r="D31" s="2" t="inlineStr"/>
+      <c r="B31" s="4" t="inlineStr"/>
+      <c r="C31" s="4" t="inlineStr"/>
+      <c r="D31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr"/>
-      <c r="C32" s="2" t="inlineStr"/>
-      <c r="D32" s="2" t="inlineStr"/>
+      <c r="B32" s="4" t="inlineStr"/>
+      <c r="C32" s="4" t="inlineStr"/>
+      <c r="D32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr"/>
-      <c r="C33" s="2" t="inlineStr"/>
-      <c r="D33" s="2" t="inlineStr"/>
+      <c r="B33" s="4" t="inlineStr"/>
+      <c r="C33" s="4" t="inlineStr"/>
+      <c r="D33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr"/>
-      <c r="C34" s="2" t="inlineStr"/>
-      <c r="D34" s="2" t="inlineStr"/>
+      <c r="B34" s="4" t="inlineStr"/>
+      <c r="C34" s="4" t="inlineStr"/>
+      <c r="D34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr"/>
-      <c r="C35" s="2" t="inlineStr"/>
-      <c r="D35" s="2" t="inlineStr"/>
+      <c r="B35" s="4" t="inlineStr"/>
+      <c r="C35" s="4" t="inlineStr"/>
+      <c r="D35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr"/>
-      <c r="C36" s="2" t="inlineStr"/>
-      <c r="D36" s="2" t="inlineStr"/>
+      <c r="B36" s="4" t="inlineStr"/>
+      <c r="C36" s="4" t="inlineStr"/>
+      <c r="D36" s="4" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr"/>
-      <c r="C37" s="2" t="inlineStr"/>
-      <c r="D37" s="2" t="inlineStr"/>
+      <c r="B37" s="4" t="inlineStr"/>
+      <c r="C37" s="4" t="inlineStr"/>
+      <c r="D37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr"/>
-      <c r="C38" s="2" t="inlineStr"/>
-      <c r="D38" s="2" t="inlineStr"/>
+      <c r="B38" s="4" t="inlineStr"/>
+      <c r="C38" s="4" t="inlineStr"/>
+      <c r="D38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr"/>
-      <c r="C39" s="2" t="inlineStr"/>
-      <c r="D39" s="2" t="inlineStr"/>
+      <c r="B39" s="4" t="inlineStr"/>
+      <c r="C39" s="4" t="inlineStr"/>
+      <c r="D39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr"/>
-      <c r="C40" s="2" t="inlineStr"/>
-      <c r="D40" s="2" t="inlineStr"/>
+      <c r="B40" s="4" t="inlineStr"/>
+      <c r="C40" s="4" t="inlineStr"/>
+      <c r="D40" s="4" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr"/>
-      <c r="C41" s="2" t="inlineStr"/>
-      <c r="D41" s="2" t="inlineStr"/>
+      <c r="B41" s="4" t="inlineStr"/>
+      <c r="C41" s="4" t="inlineStr"/>
+      <c r="D41" s="4" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr"/>
-      <c r="C42" s="2" t="inlineStr"/>
-      <c r="D42" s="2" t="inlineStr"/>
+      <c r="B42" s="4" t="inlineStr"/>
+      <c r="C42" s="4" t="inlineStr"/>
+      <c r="D42" s="4" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr"/>
-      <c r="C43" s="2" t="inlineStr"/>
-      <c r="D43" s="2" t="inlineStr"/>
+      <c r="B43" s="4" t="inlineStr"/>
+      <c r="C43" s="4" t="inlineStr"/>
+      <c r="D43" s="4" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
@@ -1487,10 +1487,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A2:A3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/RackWorks/rack_layout_top_down.xlsx
+++ b/RackWorks/rack_layout_top_down.xlsx
@@ -9,6 +9,11 @@
   <sheets>
     <sheet name="Rack_1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Rack_2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Rack_3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Rack_4" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Rack_5" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Rack_6" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Rack_7" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -30,7 +35,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -45,14 +50,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FF9999"/>
-        <bgColor rgb="00FF9999"/>
+        <fgColor rgb="001C81CE"/>
+        <bgColor rgb="001C81CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0099CCFF"/>
-        <bgColor rgb="0099CCFF"/>
+        <fgColor rgb="00BC2D7E"/>
+        <bgColor rgb="00BC2D7E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF9999"/>
+        <bgColor rgb="00FF9999"/>
       </patternFill>
     </fill>
     <fill>
@@ -63,8 +74,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001C81CE"/>
-        <bgColor rgb="001C81CE"/>
+        <fgColor rgb="0099CCFF"/>
+        <bgColor rgb="0099CCFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -107,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -125,14 +136,17 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -548,10 +562,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="n"/>
-      <c r="B3" s="8" t="n"/>
-      <c r="C3" s="8" t="n"/>
-      <c r="D3" s="8" t="n"/>
+      <c r="A3" s="9" t="n"/>
+      <c r="B3" s="9" t="n"/>
+      <c r="C3" s="9" t="n"/>
+      <c r="D3" s="9" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -572,10 +586,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="n"/>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
+      <c r="A5" s="9" t="n"/>
+      <c r="B5" s="9" t="n"/>
+      <c r="C5" s="9" t="n"/>
+      <c r="D5" s="9" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -648,198 +662,310 @@
       <c r="D12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr"/>
-      <c r="C13" s="4" t="inlineStr"/>
-      <c r="D13" s="4" t="inlineStr"/>
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>31-31</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>NVMenodes_31</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>790</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr"/>
-      <c r="C14" s="4" t="inlineStr"/>
-      <c r="D14" s="4" t="inlineStr"/>
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>30-30</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>NVMenodes_30</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>790</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr"/>
-      <c r="C15" s="4" t="inlineStr"/>
-      <c r="D15" s="4" t="inlineStr"/>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>29-29</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>NVMenodes_29</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>790</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr"/>
-      <c r="C16" s="4" t="inlineStr"/>
-      <c r="D16" s="4" t="inlineStr"/>
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>28-28</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>NVMenodes_28</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>790</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr"/>
-      <c r="C17" s="4" t="inlineStr"/>
-      <c r="D17" s="4" t="inlineStr"/>
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>27-27</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>NVMenodes_27</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>790</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>25-26</t>
+          <t>26-26</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>compute_nodes_25</t>
+          <t>NVMenodes_26</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>1350</v>
+        <v>790</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>28.7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="n"/>
-      <c r="B19" s="8" t="n"/>
-      <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="n"/>
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>25-25</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>NVMenodes_25</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>790</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>23-24</t>
+          <t>24-24</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>compute_nodes_23</t>
+          <t>NVMenodes_24</t>
         </is>
       </c>
       <c r="C20" s="5" t="n">
+        <v>790</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>23-23</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>NVMenodes_23</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>790</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>22-22</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>NVMenodes_22</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>790</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>21-21</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>NVMenodes_21</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>790</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>20-20</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>Metadata_20</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>790</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>19-19</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>Metadata_19</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>790</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>17-18</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>compute_nodes_17</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="n">
         <v>1350</v>
       </c>
-      <c r="D20" s="5" t="n">
+      <c r="D26" s="7" t="n">
         <v>28.7</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="8" t="n"/>
-      <c r="B21" s="8" t="n"/>
-      <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>19-22</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>GPU_nodes_19</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="n">
-        <v>11660</v>
-      </c>
-      <c r="D22" s="6" t="n">
-        <v>61.4</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="9" t="n"/>
-      <c r="B23" s="9" t="n"/>
-      <c r="C23" s="9" t="n"/>
-      <c r="D23" s="9" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="9" t="n"/>
-      <c r="B24" s="9" t="n"/>
-      <c r="C24" s="9" t="n"/>
-      <c r="D24" s="9" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="n"/>
-      <c r="B25" s="8" t="n"/>
-      <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr"/>
-      <c r="C26" s="4" t="inlineStr"/>
-      <c r="D26" s="4" t="inlineStr"/>
-    </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr"/>
-      <c r="C27" s="4" t="inlineStr"/>
-      <c r="D27" s="4" t="inlineStr"/>
+      <c r="A27" s="9" t="n"/>
+      <c r="B27" s="9" t="n"/>
+      <c r="C27" s="9" t="n"/>
+      <c r="D27" s="9" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr"/>
-      <c r="C28" s="4" t="inlineStr"/>
-      <c r="D28" s="4" t="inlineStr"/>
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>15-16</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>compute_nodes_15</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="n">
+        <v>1350</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>28.7</v>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr"/>
-      <c r="C29" s="4" t="inlineStr"/>
-      <c r="D29" s="4" t="inlineStr"/>
+      <c r="A29" s="9" t="n"/>
+      <c r="B29" s="9" t="n"/>
+      <c r="C29" s="9" t="n"/>
+      <c r="D29" s="9" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr"/>
-      <c r="C30" s="4" t="inlineStr"/>
-      <c r="D30" s="4" t="inlineStr"/>
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>13-14</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>compute_nodes_13</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="n">
+        <v>1350</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>28.7</v>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr"/>
-      <c r="C31" s="4" t="inlineStr"/>
-      <c r="D31" s="4" t="inlineStr"/>
+      <c r="A31" s="9" t="n"/>
+      <c r="B31" s="9" t="n"/>
+      <c r="C31" s="9" t="n"/>
+      <c r="D31" s="9" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -962,41 +1088,41 @@
       <c r="D43" s="4" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="7" t="inlineStr">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B45" s="7" t="inlineStr"/>
-      <c r="C45" s="7" t="n">
-        <v>15964</v>
-      </c>
-      <c r="D45" s="7" t="n">
-        <v>150.8</v>
+      <c r="B45" s="8" t="inlineStr"/>
+      <c r="C45" s="8" t="n">
+        <v>15924</v>
+      </c>
+      <c r="D45" s="8" t="n">
+        <v>378.1</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B22:B25"/>
-    <mergeCell ref="D22:D25"/>
+    <mergeCell ref="C30:C31"/>
     <mergeCell ref="C4:C5"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C20:C21"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="D2:D3"/>
-    <mergeCell ref="C22:C25"/>
+    <mergeCell ref="C26:C27"/>
     <mergeCell ref="D4:D5"/>
+    <mergeCell ref="A26:A27"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="C2:C3"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="D28:D29"/>
     <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="D30:D31"/>
     <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="A30:A31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1040,28 +1166,24 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>41-42</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>LAN_1__IB+400_41</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>2000</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>20</v>
-      </c>
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr"/>
+      <c r="C2" s="4" t="inlineStr"/>
+      <c r="D2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n"/>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr"/>
+      <c r="C3" s="4" t="inlineStr"/>
+      <c r="D3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -1174,34 +1296,2692 @@
       <c r="D14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr"/>
-      <c r="C15" s="4" t="inlineStr"/>
-      <c r="D15" s="4" t="inlineStr"/>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>29-29</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>NVMenodes_29</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>790</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr"/>
-      <c r="C16" s="4" t="inlineStr"/>
-      <c r="D16" s="4" t="inlineStr"/>
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>compute_nodes_27</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>1350</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>28.7</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr"/>
-      <c r="C17" s="4" t="inlineStr"/>
-      <c r="D17" s="4" t="inlineStr"/>
+      <c r="A17" s="9" t="n"/>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="9" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>compute_nodes_25</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>1350</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="n"/>
+      <c r="B19" s="9" t="n"/>
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="9" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>21-24</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>GPU_nodes_21</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="n">
+        <v>11660</v>
+      </c>
+      <c r="D20" s="10" t="n">
+        <v>61.4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="n"/>
+      <c r="B21" s="11" t="n"/>
+      <c r="C21" s="11" t="n"/>
+      <c r="D21" s="11" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="n"/>
+      <c r="B22" s="11" t="n"/>
+      <c r="C22" s="11" t="n"/>
+      <c r="D22" s="11" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="n"/>
+      <c r="B23" s="9" t="n"/>
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="9" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr"/>
+      <c r="C24" s="4" t="inlineStr"/>
+      <c r="D24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr"/>
+      <c r="C25" s="4" t="inlineStr"/>
+      <c r="D25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr"/>
+      <c r="C26" s="4" t="inlineStr"/>
+      <c r="D26" s="4" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr"/>
+      <c r="C27" s="4" t="inlineStr"/>
+      <c r="D27" s="4" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr"/>
+      <c r="C28" s="4" t="inlineStr"/>
+      <c r="D28" s="4" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr"/>
+      <c r="C29" s="4" t="inlineStr"/>
+      <c r="D29" s="4" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr"/>
+      <c r="C30" s="4" t="inlineStr"/>
+      <c r="D30" s="4" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr"/>
+      <c r="C31" s="4" t="inlineStr"/>
+      <c r="D31" s="4" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr"/>
+      <c r="C32" s="4" t="inlineStr"/>
+      <c r="D32" s="4" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr"/>
+      <c r="C33" s="4" t="inlineStr"/>
+      <c r="D33" s="4" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr"/>
+      <c r="C34" s="4" t="inlineStr"/>
+      <c r="D34" s="4" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr"/>
+      <c r="C35" s="4" t="inlineStr"/>
+      <c r="D35" s="4" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr"/>
+      <c r="C36" s="4" t="inlineStr"/>
+      <c r="D36" s="4" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr"/>
+      <c r="C37" s="4" t="inlineStr"/>
+      <c r="D37" s="4" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr"/>
+      <c r="C38" s="4" t="inlineStr"/>
+      <c r="D38" s="4" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr"/>
+      <c r="C39" s="4" t="inlineStr"/>
+      <c r="D39" s="4" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr"/>
+      <c r="C40" s="4" t="inlineStr"/>
+      <c r="D40" s="4" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr"/>
+      <c r="C41" s="4" t="inlineStr"/>
+      <c r="D41" s="4" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr"/>
+      <c r="C42" s="4" t="inlineStr"/>
+      <c r="D42" s="4" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr"/>
+      <c r="C43" s="4" t="inlineStr"/>
+      <c r="D43" s="4" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr"/>
+      <c r="C45" s="8" t="n">
+        <v>15150</v>
+      </c>
+      <c r="D45" s="8" t="n">
+        <v>138.8</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="B20:B23"/>
+    <mergeCell ref="C20:C23"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="D20:D23"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="A18:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Rack Position</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Device</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Wattage (W)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Weight (kg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr"/>
+      <c r="C2" s="4" t="inlineStr"/>
+      <c r="D2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr"/>
+      <c r="C3" s="4" t="inlineStr"/>
+      <c r="D3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr"/>
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr"/>
+      <c r="C5" s="4" t="inlineStr"/>
+      <c r="D5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr"/>
+      <c r="C6" s="4" t="inlineStr"/>
+      <c r="D6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr"/>
+      <c r="C7" s="4" t="inlineStr"/>
+      <c r="D7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr"/>
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>34-35</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>compute_nodes_34</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>1350</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="n"/>
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="9" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>32-33</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>compute_nodes_32</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>1350</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="n"/>
+      <c r="B12" s="9" t="n"/>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="9" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>30-31</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>compute_nodes_30</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>1350</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="n"/>
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="9" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>28-29</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>compute_nodes_28</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>1350</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="n"/>
+      <c r="B16" s="9" t="n"/>
+      <c r="C16" s="9" t="n"/>
+      <c r="D16" s="9" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>compute_nodes_26</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>1350</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="n"/>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="9" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>24-25</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>compute_nodes_24</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>1350</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="n"/>
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="9" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>22-23</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>compute_nodes_22</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>1350</v>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="n"/>
+      <c r="B22" s="9" t="n"/>
+      <c r="C22" s="9" t="n"/>
+      <c r="D22" s="9" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>20-21</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>compute_nodes_20</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="n">
+        <v>1350</v>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="n"/>
+      <c r="B24" s="9" t="n"/>
+      <c r="C24" s="9" t="n"/>
+      <c r="D24" s="9" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>18-19</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>compute_nodes_18</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="n">
+        <v>1350</v>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="n"/>
+      <c r="B26" s="9" t="n"/>
+      <c r="C26" s="9" t="n"/>
+      <c r="D26" s="9" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>16-17</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>compute_nodes_16</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>1350</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="n"/>
+      <c r="B28" s="9" t="n"/>
+      <c r="C28" s="9" t="n"/>
+      <c r="D28" s="9" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>14-15</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>compute_nodes_14</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="n">
+        <v>1350</v>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="n"/>
+      <c r="B30" s="9" t="n"/>
+      <c r="C30" s="9" t="n"/>
+      <c r="D30" s="9" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr"/>
+      <c r="C31" s="4" t="inlineStr"/>
+      <c r="D31" s="4" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr"/>
+      <c r="C32" s="4" t="inlineStr"/>
+      <c r="D32" s="4" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr"/>
+      <c r="C33" s="4" t="inlineStr"/>
+      <c r="D33" s="4" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr"/>
+      <c r="C34" s="4" t="inlineStr"/>
+      <c r="D34" s="4" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr"/>
+      <c r="C35" s="4" t="inlineStr"/>
+      <c r="D35" s="4" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr"/>
+      <c r="C36" s="4" t="inlineStr"/>
+      <c r="D36" s="4" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr"/>
+      <c r="C37" s="4" t="inlineStr"/>
+      <c r="D37" s="4" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr"/>
+      <c r="C38" s="4" t="inlineStr"/>
+      <c r="D38" s="4" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr"/>
+      <c r="C39" s="4" t="inlineStr"/>
+      <c r="D39" s="4" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr"/>
+      <c r="C40" s="4" t="inlineStr"/>
+      <c r="D40" s="4" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr"/>
+      <c r="C41" s="4" t="inlineStr"/>
+      <c r="D41" s="4" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr"/>
+      <c r="C42" s="4" t="inlineStr"/>
+      <c r="D42" s="4" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr"/>
+      <c r="C43" s="4" t="inlineStr"/>
+      <c r="D43" s="4" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr"/>
+      <c r="C45" s="8" t="n">
+        <v>14850</v>
+      </c>
+      <c r="D45" s="8" t="n">
+        <v>315.6999999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="44">
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="A11:A12"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Rack Position</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Device</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Wattage (W)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Weight (kg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr"/>
+      <c r="C2" s="4" t="inlineStr"/>
+      <c r="D2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr"/>
+      <c r="C3" s="4" t="inlineStr"/>
+      <c r="D3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr"/>
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr"/>
+      <c r="C5" s="4" t="inlineStr"/>
+      <c r="D5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr"/>
+      <c r="C6" s="4" t="inlineStr"/>
+      <c r="D6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr"/>
+      <c r="C7" s="4" t="inlineStr"/>
+      <c r="D7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr"/>
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr"/>
+      <c r="C9" s="4" t="inlineStr"/>
+      <c r="D9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr"/>
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr"/>
+      <c r="C11" s="4" t="inlineStr"/>
+      <c r="D11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr"/>
+      <c r="C12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr"/>
+      <c r="C13" s="4" t="inlineStr"/>
+      <c r="D13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>29-30</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>compute_nodes_29</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>1350</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="n"/>
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>compute_nodes_27</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>1350</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="n"/>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="9" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>compute_nodes_25</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>1350</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="n"/>
+      <c r="B19" s="9" t="n"/>
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="9" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>21-24</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>GPU_nodes_21</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="n">
+        <v>11660</v>
+      </c>
+      <c r="D20" s="10" t="n">
+        <v>61.4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="n"/>
+      <c r="B21" s="11" t="n"/>
+      <c r="C21" s="11" t="n"/>
+      <c r="D21" s="11" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="n"/>
+      <c r="B22" s="11" t="n"/>
+      <c r="C22" s="11" t="n"/>
+      <c r="D22" s="11" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="n"/>
+      <c r="B23" s="9" t="n"/>
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="9" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr"/>
+      <c r="C24" s="4" t="inlineStr"/>
+      <c r="D24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr"/>
+      <c r="C25" s="4" t="inlineStr"/>
+      <c r="D25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr"/>
+      <c r="C26" s="4" t="inlineStr"/>
+      <c r="D26" s="4" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr"/>
+      <c r="C27" s="4" t="inlineStr"/>
+      <c r="D27" s="4" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr"/>
+      <c r="C28" s="4" t="inlineStr"/>
+      <c r="D28" s="4" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr"/>
+      <c r="C29" s="4" t="inlineStr"/>
+      <c r="D29" s="4" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr"/>
+      <c r="C30" s="4" t="inlineStr"/>
+      <c r="D30" s="4" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr"/>
+      <c r="C31" s="4" t="inlineStr"/>
+      <c r="D31" s="4" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr"/>
+      <c r="C32" s="4" t="inlineStr"/>
+      <c r="D32" s="4" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr"/>
+      <c r="C33" s="4" t="inlineStr"/>
+      <c r="D33" s="4" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr"/>
+      <c r="C34" s="4" t="inlineStr"/>
+      <c r="D34" s="4" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr"/>
+      <c r="C35" s="4" t="inlineStr"/>
+      <c r="D35" s="4" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr"/>
+      <c r="C36" s="4" t="inlineStr"/>
+      <c r="D36" s="4" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr"/>
+      <c r="C37" s="4" t="inlineStr"/>
+      <c r="D37" s="4" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr"/>
+      <c r="C38" s="4" t="inlineStr"/>
+      <c r="D38" s="4" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr"/>
+      <c r="C39" s="4" t="inlineStr"/>
+      <c r="D39" s="4" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr"/>
+      <c r="C40" s="4" t="inlineStr"/>
+      <c r="D40" s="4" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr"/>
+      <c r="C41" s="4" t="inlineStr"/>
+      <c r="D41" s="4" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr"/>
+      <c r="C42" s="4" t="inlineStr"/>
+      <c r="D42" s="4" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr"/>
+      <c r="C43" s="4" t="inlineStr"/>
+      <c r="D43" s="4" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr"/>
+      <c r="C45" s="8" t="n">
+        <v>15710</v>
+      </c>
+      <c r="D45" s="8" t="n">
+        <v>147.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B20:B23"/>
+    <mergeCell ref="C20:C23"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="D20:D23"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="B14:B15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Rack Position</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Device</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Wattage (W)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Weight (kg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>41-42</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>LAN_2__Z_9xxx_41</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>1304</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="n"/>
+      <c r="B3" s="9" t="n"/>
+      <c r="C3" s="9" t="n"/>
+      <c r="D3" s="9" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>39-40</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>LAN_3__S_xx64_39</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="n"/>
+      <c r="B5" s="9" t="n"/>
+      <c r="C5" s="9" t="n"/>
+      <c r="D5" s="9" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr"/>
+      <c r="C6" s="4" t="inlineStr"/>
+      <c r="D6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr"/>
+      <c r="C7" s="4" t="inlineStr"/>
+      <c r="D7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr"/>
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr"/>
+      <c r="C9" s="4" t="inlineStr"/>
+      <c r="D9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr"/>
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr"/>
+      <c r="C11" s="4" t="inlineStr"/>
+      <c r="D11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>31-32</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>compute_nodes_31</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>1350</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="n"/>
+      <c r="B13" s="9" t="n"/>
+      <c r="C13" s="9" t="n"/>
+      <c r="D13" s="9" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>29-30</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>compute_nodes_29</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>1350</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="n"/>
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>compute_nodes_27</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>1350</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="n"/>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="9" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>compute_nodes_25</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>1350</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="n"/>
+      <c r="B19" s="9" t="n"/>
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="9" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>23-24</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>compute_nodes_23</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>1350</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="n"/>
+      <c r="B21" s="9" t="n"/>
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="9" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>21-22</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>compute_nodes_21</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="n">
+        <v>1350</v>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="n"/>
+      <c r="B23" s="9" t="n"/>
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="9" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>19-20</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>compute_nodes_19</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>1350</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="n"/>
+      <c r="B25" s="9" t="n"/>
+      <c r="C25" s="9" t="n"/>
+      <c r="D25" s="9" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>17-18</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>compute_nodes_17</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>1350</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="n"/>
+      <c r="B27" s="9" t="n"/>
+      <c r="C27" s="9" t="n"/>
+      <c r="D27" s="9" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>15-16</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>compute_nodes_15</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="n">
+        <v>1350</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="n"/>
+      <c r="B29" s="9" t="n"/>
+      <c r="C29" s="9" t="n"/>
+      <c r="D29" s="9" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>13-14</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>compute_nodes_13</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="n">
+        <v>1350</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="n"/>
+      <c r="B31" s="9" t="n"/>
+      <c r="C31" s="9" t="n"/>
+      <c r="D31" s="9" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr"/>
+      <c r="C32" s="4" t="inlineStr"/>
+      <c r="D32" s="4" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr"/>
+      <c r="C33" s="4" t="inlineStr"/>
+      <c r="D33" s="4" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr"/>
+      <c r="C34" s="4" t="inlineStr"/>
+      <c r="D34" s="4" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr"/>
+      <c r="C35" s="4" t="inlineStr"/>
+      <c r="D35" s="4" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr"/>
+      <c r="C36" s="4" t="inlineStr"/>
+      <c r="D36" s="4" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr"/>
+      <c r="C37" s="4" t="inlineStr"/>
+      <c r="D37" s="4" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr"/>
+      <c r="C38" s="4" t="inlineStr"/>
+      <c r="D38" s="4" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr"/>
+      <c r="C39" s="4" t="inlineStr"/>
+      <c r="D39" s="4" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr"/>
+      <c r="C40" s="4" t="inlineStr"/>
+      <c r="D40" s="4" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr"/>
+      <c r="C41" s="4" t="inlineStr"/>
+      <c r="D41" s="4" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr"/>
+      <c r="C42" s="4" t="inlineStr"/>
+      <c r="D42" s="4" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr"/>
+      <c r="C43" s="4" t="inlineStr"/>
+      <c r="D43" s="4" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr"/>
+      <c r="C45" s="8" t="n">
+        <v>15104</v>
+      </c>
+      <c r="D45" s="8" t="n">
+        <v>318.9999999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="48">
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="D22:D23"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Rack Position</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Device</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Wattage (W)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Weight (kg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr"/>
+      <c r="C2" s="4" t="inlineStr"/>
+      <c r="D2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr"/>
+      <c r="C3" s="4" t="inlineStr"/>
+      <c r="D3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr"/>
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr"/>
+      <c r="C5" s="4" t="inlineStr"/>
+      <c r="D5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr"/>
+      <c r="C6" s="4" t="inlineStr"/>
+      <c r="D6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr"/>
+      <c r="C7" s="4" t="inlineStr"/>
+      <c r="D7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr"/>
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr"/>
+      <c r="C9" s="4" t="inlineStr"/>
+      <c r="D9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr"/>
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr"/>
+      <c r="C11" s="4" t="inlineStr"/>
+      <c r="D11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr"/>
+      <c r="C12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr"/>
+      <c r="C13" s="4" t="inlineStr"/>
+      <c r="D13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>29-30</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>compute_nodes_29</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>1350</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="n"/>
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>compute_nodes_27</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>1350</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="n"/>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="9" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>compute_nodes_25</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>1350</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="n"/>
+      <c r="B19" s="9" t="n"/>
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="9" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>23-24</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>compute_nodes_23</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>1350</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="n"/>
+      <c r="B21" s="9" t="n"/>
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="9" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>21-22</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>compute_nodes_21</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="n">
+        <v>1350</v>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="n"/>
+      <c r="B23" s="9" t="n"/>
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="9" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr"/>
+      <c r="C24" s="4" t="inlineStr"/>
+      <c r="D24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr"/>
+      <c r="C25" s="4" t="inlineStr"/>
+      <c r="D25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr"/>
+      <c r="C26" s="4" t="inlineStr"/>
+      <c r="D26" s="4" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr"/>
+      <c r="C27" s="4" t="inlineStr"/>
+      <c r="D27" s="4" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr"/>
+      <c r="C28" s="4" t="inlineStr"/>
+      <c r="D28" s="4" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr"/>
+      <c r="C29" s="4" t="inlineStr"/>
+      <c r="D29" s="4" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr"/>
+      <c r="C30" s="4" t="inlineStr"/>
+      <c r="D30" s="4" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr"/>
+      <c r="C31" s="4" t="inlineStr"/>
+      <c r="D31" s="4" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr"/>
+      <c r="C32" s="4" t="inlineStr"/>
+      <c r="D32" s="4" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr"/>
+      <c r="C33" s="4" t="inlineStr"/>
+      <c r="D33" s="4" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr"/>
+      <c r="C34" s="4" t="inlineStr"/>
+      <c r="D34" s="4" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr"/>
+      <c r="C35" s="4" t="inlineStr"/>
+      <c r="D35" s="4" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr"/>
+      <c r="C36" s="4" t="inlineStr"/>
+      <c r="D36" s="4" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr"/>
+      <c r="C37" s="4" t="inlineStr"/>
+      <c r="D37" s="4" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr"/>
+      <c r="C38" s="4" t="inlineStr"/>
+      <c r="D38" s="4" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr"/>
+      <c r="C39" s="4" t="inlineStr"/>
+      <c r="D39" s="4" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr"/>
+      <c r="C40" s="4" t="inlineStr"/>
+      <c r="D40" s="4" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr"/>
+      <c r="C41" s="4" t="inlineStr"/>
+      <c r="D41" s="4" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr"/>
+      <c r="C42" s="4" t="inlineStr"/>
+      <c r="D42" s="4" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr"/>
+      <c r="C43" s="4" t="inlineStr"/>
+      <c r="D43" s="4" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr"/>
+      <c r="C45" s="8" t="n">
+        <v>6750</v>
+      </c>
+      <c r="D45" s="8" t="n">
+        <v>143.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="20">
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D22:D23"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Rack Position</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Device</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Wattage (W)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Weight (kg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr"/>
+      <c r="C2" s="4" t="inlineStr"/>
+      <c r="D2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr"/>
+      <c r="C3" s="4" t="inlineStr"/>
+      <c r="D3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr"/>
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr"/>
+      <c r="C5" s="4" t="inlineStr"/>
+      <c r="D5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr"/>
+      <c r="C6" s="4" t="inlineStr"/>
+      <c r="D6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr"/>
+      <c r="C7" s="4" t="inlineStr"/>
+      <c r="D7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr"/>
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr"/>
+      <c r="C9" s="4" t="inlineStr"/>
+      <c r="D9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr"/>
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr"/>
+      <c r="C11" s="4" t="inlineStr"/>
+      <c r="D11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr"/>
+      <c r="C12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr"/>
+      <c r="C13" s="4" t="inlineStr"/>
+      <c r="D13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>27-30</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>GPU_nodes_27</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="n">
+        <v>11660</v>
+      </c>
+      <c r="D14" s="10" t="n">
+        <v>61.4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n"/>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n"/>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n"/>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -1254,22 +4034,14 @@
       <c r="D22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>21-21</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>NVMenodes_21</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="n">
-        <v>1128</v>
-      </c>
-      <c r="D23" s="10" t="n">
-        <v>20</v>
-      </c>
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr"/>
+      <c r="C23" s="4" t="inlineStr"/>
+      <c r="D23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -1472,25 +4244,25 @@
       <c r="D43" s="4" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="7" t="inlineStr">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B45" s="7" t="inlineStr"/>
-      <c r="C45" s="7" t="n">
-        <v>3128</v>
-      </c>
-      <c r="D45" s="7" t="n">
-        <v>40</v>
+      <c r="B45" s="8" t="inlineStr"/>
+      <c r="C45" s="8" t="n">
+        <v>11660</v>
+      </c>
+      <c r="D45" s="8" t="n">
+        <v>61.4</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="D14:D17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
